--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.15-16-18-identity-access-management/WKBK/90_workbooks/ISMS-IMP-A.5.15-16-18.S5_Lifecycle_Compliance_Detailed_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.15-16-18-identity-access-management/WKBK/90_workbooks/ISMS-IMP-A.5.15-16-18.S5_Lifecycle_Compliance_Detailed_20260208.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08.02.2026 11:48</t>
+          <t>08.02.2026 12:25</t>
         </is>
       </c>
     </row>
@@ -1220,36 +1220,36 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>carol.garcia</t>
+          <t>bob.williams</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Carol Garcia</t>
+          <t>Bob Williams</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Specialist</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>01.11.2025</t>
+          <t>12.09.2025</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>31.10.2025</t>
+          <t>10.09.2025</t>
         </is>
       </c>
       <c r="I6" s="9" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J6" s="9" t="n">
         <v>0</v>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>grace.smith</t>
+          <t>grace.garcia</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Grace Smith</t>
+          <t>Grace Garcia</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Specialist</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>24.12.2025</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>23.12.2025</t>
+          <t>07.11.2025</t>
         </is>
       </c>
       <c r="I7" s="9" t="n">
@@ -1328,32 +1328,32 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>frank.brown</t>
+          <t>bob.jones</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Frank Brown</t>
+          <t>Bob Jones</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Specialist</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>27.10.2025</t>
+          <t>14.09.2025</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>25.10.2025</t>
+          <t>12.09.2025</t>
         </is>
       </c>
       <c r="I8" s="9" t="n">
@@ -1382,36 +1382,36 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>bob.brown</t>
+          <t>bob.jones</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Bob Brown</t>
+          <t>Bob Jones</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Representative</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>05.01.2026</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>04.01.2026</t>
+          <t>27.11.2025</t>
         </is>
       </c>
       <c r="I9" s="9" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J9" s="9" t="n">
         <v>0</v>
@@ -1436,36 +1436,36 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>carol.garcia</t>
+          <t>bob.garcia</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Carol Garcia</t>
+          <t>Bob Garcia</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Specialist</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>30.08.2025</t>
+          <t>11.10.2025</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>30.08.2025</t>
+          <t>10.10.2025</t>
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J10" s="9" t="n">
         <v>0</v>
@@ -1490,36 +1490,36 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>alice.johnson</t>
+          <t>alice.smith</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Alice Johnson</t>
+          <t>Alice Smith</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Representative</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>24.12.2025</t>
+          <t>29.08.2025</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>24.12.2025</t>
+          <t>27.08.2025</t>
         </is>
       </c>
       <c r="I11" s="9" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J11" s="9" t="n">
         <v>0</v>
@@ -1544,36 +1544,36 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>bob.smith</t>
+          <t>david.johnson</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Bob Smith</t>
+          <t>David Johnson</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Representative</t>
+          <t>Specialist</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>15.08.2025</t>
+          <t>09.01.2026</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>15.08.2025</t>
+          <t>07.01.2026</t>
         </is>
       </c>
       <c r="I12" s="9" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J12" s="9" t="n">
         <v>0</v>
@@ -1598,12 +1598,12 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>grace.brown</t>
+          <t>david.williams</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Grace Brown</t>
+          <t>David Williams</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1618,12 +1618,12 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>17.12.2025</t>
+          <t>06.10.2025</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>15.12.2025</t>
+          <t>04.10.2025</t>
         </is>
       </c>
       <c r="I13" s="9" t="n">
@@ -1652,36 +1652,36 @@
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>alice.smith</t>
+          <t>grace.williams</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Alice Smith</t>
+          <t>Grace Williams</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Coordinator</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>19.11.2025</t>
+          <t>17.12.2025</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>18.11.2025</t>
+          <t>17.12.2025</t>
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J14" s="9" t="n">
         <v>0</v>
@@ -1706,36 +1706,36 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>frank.jones</t>
+          <t>grace.garcia</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Frank Jones</t>
+          <t>Grace Garcia</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Coordinator</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>28.10.2025</t>
+          <t>19.09.2025</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>26.10.2025</t>
+          <t>19.09.2025</t>
         </is>
       </c>
       <c r="I15" s="9" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J15" s="9" t="n">
         <v>0</v>
@@ -1760,17 +1760,17 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>alice.garcia</t>
+          <t>alice.smith</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Alice Garcia</t>
+          <t>Alice Smith</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
@@ -1780,16 +1780,16 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>13.08.2025</t>
+          <t>20.10.2025</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>12.08.2025</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J16" s="9" t="n">
         <v>0</v>
@@ -1814,32 +1814,32 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>bob.smith</t>
+          <t>david.jones</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Bob Smith</t>
+          <t>David Jones</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Specialist</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>24.11.2025</t>
+          <t>10.11.2025</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>23.11.2025</t>
+          <t>09.11.2025</t>
         </is>
       </c>
       <c r="I17" s="9" t="n">
@@ -1868,32 +1868,32 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>grace.jones</t>
+          <t>alice.brown</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Grace Jones</t>
+          <t>Alice Brown</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Representative</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>02.12.2025</t>
+          <t>29.10.2025</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>30.11.2025</t>
+          <t>27.10.2025</t>
         </is>
       </c>
       <c r="I18" s="9" t="n">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>bob.jones</t>
+          <t>david.smith</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Bob Jones</t>
+          <t>David Smith</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -1937,35 +1937,31 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Specialist</t>
+          <t>Representative</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>16.12.2025</t>
+          <t>17.10.2025</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>23.12.2025</t>
+          <t>17.10.2025</t>
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="11" t="inlineStr">
-        <is>
-          <t>Non-Compliant</t>
-        </is>
-      </c>
-      <c r="L19" s="9" t="inlineStr">
-        <is>
-          <t>Provisioned 7 day(s) late</t>
-        </is>
-      </c>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -1980,32 +1976,32 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>emma.williams</t>
+          <t>carol.brown</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Emma Williams</t>
+          <t>Carol Brown</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Specialist</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>10.11.2025</t>
+          <t>02.10.2025</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>08.11.2025</t>
+          <t>30.09.2025</t>
         </is>
       </c>
       <c r="I20" s="9" t="n">
@@ -2034,17 +2030,17 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>henry.jones</t>
+          <t>bob.smith</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Henry Jones</t>
+          <t>Bob Smith</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
@@ -2054,16 +2050,16 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>20.08.2025</t>
+          <t>19.08.2025</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>20.08.2025</t>
+          <t>18.08.2025</t>
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J21" s="9" t="n">
         <v>0</v>
@@ -2088,12 +2084,12 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>carol.jones</t>
+          <t>carol.garcia</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Carol Jones</t>
+          <t>Carol Garcia</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -2103,17 +2099,17 @@
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>Representative</t>
+          <t>Specialist</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>30.10.2025</t>
+          <t>10.12.2025</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>28.10.2025</t>
+          <t>08.12.2025</t>
         </is>
       </c>
       <c r="I22" s="9" t="n">
@@ -2142,12 +2138,12 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>frank.johnson</t>
+          <t>emma.smith</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Frank Johnson</t>
+          <t>Emma Smith</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -2157,17 +2153,17 @@
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Specialist</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>12.10.2025</t>
+          <t>01.09.2025</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>12.10.2025</t>
+          <t>01.09.2025</t>
         </is>
       </c>
       <c r="I23" s="9" t="n">
@@ -2196,46 +2192,50 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>frank.smith</t>
+          <t>henry.garcia</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Frank Smith</t>
+          <t>Henry Garcia</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Representative</t>
+          <t>Specialist</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>22.10.2025</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>21.10.2025</t>
+          <t>16.11.2025</t>
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="10" t="inlineStr">
-        <is>
-          <t>Compliant</t>
-        </is>
-      </c>
-      <c r="L24" s="9" t="n"/>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>Provisioned 5 day(s) late</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
@@ -2250,17 +2250,17 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>emma.williams</t>
+          <t>david.jones</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Emma Williams</t>
+          <t>David Jones</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
@@ -2270,26 +2270,30 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>30.10.2025</t>
+          <t>25.08.2025</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>29.10.2025</t>
+          <t>28.08.2025</t>
         </is>
       </c>
       <c r="I25" s="9" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="J25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K25" s="10" t="inlineStr">
-        <is>
-          <t>Compliant</t>
-        </is>
-      </c>
-      <c r="L25" s="9" t="n"/>
+      <c r="K25" s="11" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>Provisioned 3 day(s) late</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
@@ -2304,32 +2308,32 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>henry.jones</t>
+          <t>david.williams</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Henry Jones</t>
+          <t>David Williams</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>11.12.2025</t>
+          <t>15.08.2025</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>11.12.2025</t>
+          <t>15.08.2025</t>
         </is>
       </c>
       <c r="I26" s="9" t="n">
@@ -2358,32 +2362,32 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>henry.jones</t>
+          <t>bob.williams</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Henry Jones</t>
+          <t>Bob Williams</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Specialist</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>30.09.2025</t>
+          <t>20.12.2025</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>28.09.2025</t>
+          <t>18.12.2025</t>
         </is>
       </c>
       <c r="I27" s="9" t="n">
@@ -2412,46 +2416,50 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>alice.johnson</t>
+          <t>david.garcia</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Alice Johnson</t>
+          <t>David Garcia</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Representative</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>09.11.2025</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>09.11.2025</t>
+          <t>02.12.2025</t>
         </is>
       </c>
       <c r="I28" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K28" s="10" t="inlineStr">
-        <is>
-          <t>Compliant</t>
-        </is>
-      </c>
-      <c r="L28" s="9" t="n"/>
+      <c r="K28" s="11" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="inlineStr">
+        <is>
+          <t>Provisioned 2 day(s) late</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
@@ -2466,36 +2474,36 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>david.garcia</t>
+          <t>emma.brown</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>David Garcia</t>
+          <t>Emma Brown</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Coordinator</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>01.12.2025</t>
+          <t>03.01.2026</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>30.11.2025</t>
+          <t>01.01.2026</t>
         </is>
       </c>
       <c r="I29" s="9" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J29" s="9" t="n">
         <v>0</v>
@@ -2520,32 +2528,32 @@
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>david.johnson</t>
+          <t>grace.brown</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>David Johnson</t>
+          <t>Grace Brown</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>23.12.2025</t>
+          <t>19.09.2025</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>23.12.2025</t>
+          <t>19.09.2025</t>
         </is>
       </c>
       <c r="I30" s="9" t="n">
@@ -2574,46 +2582,50 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>emma.jones</t>
+          <t>alice.jones</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Emma Jones</t>
+          <t>Alice Jones</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Representative</t>
+          <t>Coordinator</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>03.10.2025</t>
+          <t>19.11.2025</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>01.10.2025</t>
+          <t>21.11.2025</t>
         </is>
       </c>
       <c r="I31" s="9" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="J31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K31" s="10" t="inlineStr">
-        <is>
-          <t>Compliant</t>
-        </is>
-      </c>
-      <c r="L31" s="9" t="n"/>
+      <c r="K31" s="11" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>Provisioned 2 day(s) late</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
@@ -2628,50 +2640,46 @@
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>david.brown</t>
+          <t>david.garcia</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>David Brown</t>
+          <t>David Garcia</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>Coordinator</t>
+          <t>Representative</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>19.10.2025</t>
+          <t>26.08.2025</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>22.10.2025</t>
+          <t>25.08.2025</t>
         </is>
       </c>
       <c r="I32" s="9" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="J32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K32" s="11" t="inlineStr">
-        <is>
-          <t>Non-Compliant</t>
-        </is>
-      </c>
-      <c r="L32" s="9" t="inlineStr">
-        <is>
-          <t>Provisioned 3 day(s) late</t>
-        </is>
-      </c>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
@@ -2686,36 +2694,36 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>emma.garcia</t>
+          <t>henry.johnson</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Emma Garcia</t>
+          <t>Henry Johnson</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>Representative</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>20.09.2025</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>19.09.2025</t>
         </is>
       </c>
       <c r="I33" s="9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J33" s="9" t="n">
         <v>0</v>
@@ -2740,50 +2748,46 @@
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>emma.garcia</t>
+          <t>henry.brown</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Emma Garcia</t>
+          <t>Henry Brown</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>Specialist</t>
+          <t>Coordinator</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>21.12.2025</t>
+          <t>13.11.2025</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>26.12.2025</t>
+          <t>11.11.2025</t>
         </is>
       </c>
       <c r="I34" s="9" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="J34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K34" s="11" t="inlineStr">
-        <is>
-          <t>Non-Compliant</t>
-        </is>
-      </c>
-      <c r="L34" s="9" t="inlineStr">
-        <is>
-          <t>Provisioned 5 day(s) late</t>
-        </is>
-      </c>
+      <c r="K34" s="10" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
@@ -2798,46 +2802,50 @@
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>carol.jones</t>
+          <t>emma.johnson</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Carol Jones</t>
+          <t>Emma Johnson</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>Representative</t>
+          <t>Specialist</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>20.08.2025</t>
+          <t>11.09.2025</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>19.08.2025</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K35" s="10" t="inlineStr">
-        <is>
-          <t>Compliant</t>
-        </is>
-      </c>
-      <c r="L35" s="9" t="n"/>
+      <c r="K35" s="11" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>Provisioned 7 day(s) late</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
@@ -2852,12 +2860,12 @@
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>emma.jones</t>
+          <t>henry.garcia</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Emma Jones</t>
+          <t>Henry Garcia</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -2872,12 +2880,12 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>27.09.2025</t>
+          <t>17.08.2025</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>27.09.2025</t>
+          <t>17.08.2025</t>
         </is>
       </c>
       <c r="I36" s="9" t="n">
@@ -2906,36 +2914,36 @@
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>frank.williams</t>
+          <t>grace.jones</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Frank Williams</t>
+          <t>Grace Jones</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Coordinator</t>
+          <t>Representative</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>15.08.2025</t>
+          <t>15.11.2025</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>13.08.2025</t>
+          <t>15.11.2025</t>
         </is>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J37" s="9" t="n">
         <v>0</v>
@@ -2960,32 +2968,32 @@
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>henry.williams</t>
+          <t>frank.williams</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Henry Williams</t>
+          <t>Frank Williams</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>Specialist</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>01.09.2025</t>
+          <t>16.12.2025</t>
         </is>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>30.08.2025</t>
+          <t>14.12.2025</t>
         </is>
       </c>
       <c r="I38" s="9" t="n">
@@ -3014,36 +3022,36 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>alice.jones</t>
+          <t>frank.jones</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Alice Jones</t>
+          <t>Frank Jones</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>Representative</t>
+          <t>Specialist</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>29.10.2025</t>
+          <t>16.11.2025</t>
         </is>
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>29.10.2025</t>
+          <t>15.11.2025</t>
         </is>
       </c>
       <c r="I39" s="9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J39" s="9" t="n">
         <v>0</v>
@@ -3068,36 +3076,36 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>grace.garcia</t>
+          <t>alice.johnson</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Grace Garcia</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Coordinator</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>10.09.2025</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>08.09.2025</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="I40" s="9" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J40" s="9" t="n">
         <v>0</v>
@@ -3137,31 +3145,35 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
-          <t>02.11.2025</t>
+          <t>26.11.2025</t>
         </is>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>31.10.2025</t>
+          <t>03.12.2025</t>
         </is>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-2</v>
+        <v>7</v>
       </c>
       <c r="J41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K41" s="10" t="inlineStr">
-        <is>
-          <t>Compliant</t>
-        </is>
-      </c>
-      <c r="L41" s="9" t="n"/>
+      <c r="K41" s="11" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
+        </is>
+      </c>
+      <c r="L41" s="9" t="inlineStr">
+        <is>
+          <t>Provisioned 7 day(s) late</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
@@ -3176,36 +3188,36 @@
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>david.smith</t>
+          <t>carol.brown</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>David Smith</t>
+          <t>Carol Brown</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>Representative</t>
+          <t>Specialist</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>02.09.2025</t>
+          <t>27.08.2025</t>
         </is>
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>31.08.2025</t>
+          <t>27.08.2025</t>
         </is>
       </c>
       <c r="I42" s="9" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J42" s="9" t="n">
         <v>0</v>
@@ -3230,17 +3242,17 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>emma.williams</t>
+          <t>emma.jones</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Emma Williams</t>
+          <t>Emma Jones</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
@@ -3250,30 +3262,26 @@
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>06.12.2025</t>
+          <t>12.12.2025</t>
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
-          <t>11.12.2025</t>
+          <t>10.12.2025</t>
         </is>
       </c>
       <c r="I43" s="9" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="J43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K43" s="11" t="inlineStr">
-        <is>
-          <t>Non-Compliant</t>
-        </is>
-      </c>
-      <c r="L43" s="9" t="inlineStr">
-        <is>
-          <t>Provisioned 5 day(s) late</t>
-        </is>
-      </c>
+      <c r="K43" s="10" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
@@ -3288,17 +3296,17 @@
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>frank.jones</t>
+          <t>david.jones</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Frank Jones</t>
+          <t>David Jones</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr">
@@ -3308,12 +3316,12 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>20.12.2025</t>
+          <t>24.09.2025</t>
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
-          <t>18.12.2025</t>
+          <t>22.09.2025</t>
         </is>
       </c>
       <c r="I44" s="9" t="n">
@@ -3342,50 +3350,46 @@
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>henry.garcia</t>
+          <t>emma.jones</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Henry Garcia</t>
+          <t>Emma Jones</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>Coordinator</t>
+          <t>Representative</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>27.12.2025</t>
         </is>
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
-          <t>12.11.2025</t>
+          <t>27.12.2025</t>
         </is>
       </c>
       <c r="I45" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="K45" s="11" t="inlineStr">
-        <is>
-          <t>Non-Compliant</t>
-        </is>
-      </c>
-      <c r="L45" s="9" t="inlineStr">
-        <is>
-          <t>Provisioned 1 day(s) late</t>
-        </is>
-      </c>
+      <c r="K45" s="10" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3514,17 +3518,17 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>henry.johnson</t>
+          <t>alice.smith</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Henry Johnson</t>
+          <t>Alice Smith</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Promotion</t>
+          <t>Team Reassignment</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -3539,27 +3543,23 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>08.12.2025</t>
+          <t>13.11.2025</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>19.12.2025</t>
+          <t>13.11.2025</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="K6" s="12" t="inlineStr">
-        <is>
-          <t>Delayed</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>Access update delayed 11 day(s)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -3574,41 +3574,41 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>emma.garcia</t>
+          <t>alice.johnson</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Emma Garcia</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Team Reassignment</t>
+          <t>Department Transfer</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>28.01.2026</t>
+          <t>14.11.2025</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>30.01.2026</t>
+          <t>14.11.2025</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" s="10" t="inlineStr">
         <is>
@@ -3630,41 +3630,41 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>carol.smith</t>
+          <t>frank.jones</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Carol Smith</t>
+          <t>Frank Jones</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Team Reassignment</t>
+          <t>Role Change</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>16.12.2025</t>
+          <t>16.01.2026</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>19.12.2025</t>
+          <t>17.01.2026</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K8" s="10" t="inlineStr">
         <is>
@@ -3686,17 +3686,17 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>alice.jones</t>
+          <t>emma.garcia</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Alice Jones</t>
+          <t>Emma Garcia</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Role Change</t>
+          <t>Department Transfer</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -3706,21 +3706,21 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>11.11.2025</t>
+          <t>15.12.2025</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>14.11.2025</t>
+          <t>15.12.2025</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="10" t="inlineStr">
         <is>
@@ -3742,37 +3742,37 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>david.williams</t>
+          <t>david.johnson</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>David Williams</t>
+          <t>David Johnson</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Team Reassignment</t>
+          <t>Department Transfer</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>30.01.2026</t>
+          <t>23.12.2025</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>02.02.2026</t>
+          <t>26.12.2025</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
@@ -3798,48 +3798,52 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>henry.smith</t>
+          <t>carol.garcia</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Henry Smith</t>
+          <t>Carol Garcia</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Role Change</t>
+          <t>Department Transfer</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>29.11.2025</t>
+          <t>16.11.2025</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>29.11.2025</t>
+          <t>24.11.2025</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t>Compliant</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="K11" s="12" t="inlineStr">
+        <is>
+          <t>Delayed</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>Access update delayed 8 day(s)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
@@ -3854,12 +3858,12 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>henry.williams</t>
+          <t>henry.johnson</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Henry Williams</t>
+          <t>Henry Johnson</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -3869,26 +3873,26 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>17.01.2026</t>
+          <t>12.01.2026</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>17.01.2026</t>
+          <t>15.01.2026</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K12" s="10" t="inlineStr">
         <is>
@@ -3910,12 +3914,12 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>carol.brown</t>
+          <t>bob.brown</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Carol Brown</t>
+          <t>Bob Brown</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -3930,21 +3934,21 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>24.11.2025</t>
+          <t>31.12.2025</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>29.11.2025</t>
+          <t>07.01.2026</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
@@ -3953,7 +3957,7 @@
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>Access update delayed 5 day(s)</t>
+          <t>Access update delayed 7 day(s)</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3984,7 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Department Transfer</t>
+          <t>Team Reassignment</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
@@ -3990,32 +3994,28 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>07.01.2026</t>
+          <t>27.11.2025</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>21.01.2026</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="K14" s="12" t="inlineStr">
-        <is>
-          <t>Delayed</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>Access update delayed 14 day(s)</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -4030,41 +4030,41 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>alice.williams</t>
+          <t>henry.brown</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Alice Williams</t>
+          <t>Henry Brown</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Team Reassignment</t>
+          <t>Role Change</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>10.11.2025</t>
+          <t>16.01.2026</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>10.11.2025</t>
+          <t>17.01.2026</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
@@ -4086,52 +4086,48 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>grace.brown</t>
+          <t>emma.jones</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Grace Brown</t>
+          <t>Emma Jones</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Team Reassignment</t>
+          <t>Role Change</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>23.01.2026</t>
+          <t>12.01.2026</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>05.02.2026</t>
+          <t>12.01.2026</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="K16" s="12" t="inlineStr">
-        <is>
-          <t>Delayed</t>
-        </is>
-      </c>
-      <c r="L16" s="9" t="inlineStr">
-        <is>
-          <t>Access update delayed 13 day(s)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -4146,17 +4142,17 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>henry.williams</t>
+          <t>bob.johnson</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Henry Williams</t>
+          <t>Bob Johnson</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Promotion</t>
+          <t>Department Transfer</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
@@ -4171,16 +4167,16 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>04.12.2025</t>
+          <t>20.12.2025</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>05.12.2025</t>
+          <t>22.12.2025</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" s="10" t="inlineStr">
         <is>
@@ -4202,12 +4198,12 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>bob.smith</t>
+          <t>frank.williams</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Bob Smith</t>
+          <t>Frank Williams</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -4217,22 +4213,22 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>14.12.2025</t>
+          <t>10.12.2025</t>
         </is>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>16.12.2025</t>
+          <t>12.12.2025</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
@@ -4268,7 +4264,7 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Department Transfer</t>
+          <t>Promotion</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
@@ -4278,21 +4274,21 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>18.01.2026</t>
+          <t>26.11.2025</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>20.01.2026</t>
+          <t>26.11.2025</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" s="10" t="inlineStr">
         <is>
@@ -4314,41 +4310,41 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>henry.garcia</t>
+          <t>bob.garcia</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Henry Garcia</t>
+          <t>Bob Garcia</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Role Change</t>
+          <t>Promotion</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>13.11.2025</t>
+          <t>10.12.2025</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>15.11.2025</t>
+          <t>13.12.2025</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" s="10" t="inlineStr">
         <is>
@@ -4370,12 +4366,12 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>henry.jones</t>
+          <t>david.williams</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Henry Jones</t>
+          <t>David Williams</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -4385,7 +4381,7 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
@@ -4395,16 +4391,16 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>29.01.2026</t>
+          <t>18.01.2026</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>29.01.2026</t>
+          <t>21.01.2026</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
@@ -4426,37 +4422,37 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>alice.brown</t>
+          <t>alice.smith</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Alice Brown</t>
+          <t>Alice Smith</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Role Change</t>
+          <t>Promotion</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>17.01.2026</t>
+          <t>23.12.2025</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>18.01.2026</t>
+          <t>24.12.2025</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
@@ -4482,37 +4478,37 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>grace.brown</t>
+          <t>bob.smith</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Grace Brown</t>
+          <t>Bob Smith</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Team Reassignment</t>
+          <t>Role Change</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>17.12.2025</t>
+          <t>10.11.2025</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>19.12.2025</t>
+          <t>12.11.2025</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
@@ -4548,27 +4544,27 @@
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>Promotion</t>
+          <t>Department Transfer</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>03.12.2025</t>
+          <t>13.01.2026</t>
         </is>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>04.12.2025</t>
+          <t>14.01.2026</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
@@ -4594,12 +4590,12 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>david.jones</t>
+          <t>emma.brown</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>David Jones</t>
+          <t>Emma Brown</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -4609,33 +4605,37 @@
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>18.01.2026</t>
+          <t>12.01.2026</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>19.01.2026</t>
+          <t>22.01.2026</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" s="10" t="inlineStr">
-        <is>
-          <t>Compliant</t>
-        </is>
-      </c>
-      <c r="L25" s="9" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="K25" s="12" t="inlineStr">
+        <is>
+          <t>Delayed</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>Access update delayed 10 day(s)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4764,17 +4764,17 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>alice.jones</t>
+          <t>carol.jones</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Alice Jones</t>
+          <t>Carol Jones</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -4784,11 +4784,11 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>07.02.2026 17:48</t>
+          <t>07.02.2026 14:25</t>
         </is>
       </c>
       <c r="H6" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I6" s="9" t="n">
         <v>24</v>
@@ -4818,27 +4818,27 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>carol.brown</t>
+          <t>frank.williams</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Carol Brown</t>
+          <t>Frank Williams</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>21.12.2025</t>
+          <t>26.12.2025</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>21.12.2025 20:48</t>
+          <t>26.12.2025 21:25</t>
         </is>
       </c>
       <c r="H7" s="9" t="n">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>emma.brown</t>
+          <t>alice.johnson</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Emma Brown</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -4887,16 +4887,16 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>14.12.2025</t>
+          <t>04.01.2026</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>14.12.2025 17:48</t>
+          <t>04.01.2026 12:25</t>
         </is>
       </c>
       <c r="H8" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I8" s="9" t="n">
         <v>24</v>
@@ -4926,46 +4926,50 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>david.brown</t>
+          <t>alice.brown</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>David Brown</t>
+          <t>Alice Brown</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>12.01.2026</t>
+          <t>18.12.2025</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>12.01.2026 13:48</t>
+          <t>28.12.2025 12:25</t>
         </is>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2</v>
+        <v>240</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="J9" s="10" t="inlineStr">
-        <is>
-          <t>Compliant</t>
-        </is>
-      </c>
-      <c r="K9" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>Terminated user retained access for 10 day(s) - SECURITY RISK</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
@@ -4980,27 +4984,27 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>alice.jones</t>
+          <t>carol.johnson</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Alice Jones</t>
+          <t>Carol Johnson</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>11.12.2025</t>
+          <t>30.01.2026</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>11.12.2025 22:48</t>
+          <t>30.01.2026 23:25</t>
         </is>
       </c>
       <c r="H10" s="9" t="n">
@@ -5034,31 +5038,31 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>bob.garcia</t>
+          <t>david.garcia</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Bob Garcia</t>
+          <t>David Garcia</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>22.01.2026</t>
+          <t>08.01.2026</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>22.01.2026 16:48</t>
+          <t>08.01.2026 14:25</t>
         </is>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I11" s="9" t="n">
         <v>24</v>
@@ -5088,31 +5092,31 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>david.garcia</t>
+          <t>david.smith</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>David Garcia</t>
+          <t>David Smith</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>22.01.2026</t>
+          <t>15.12.2025</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>22.01.2026 12:48</t>
+          <t>15.12.2025 21:25</t>
         </is>
       </c>
       <c r="H12" s="9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I12" s="9" t="n">
         <v>24</v>
@@ -5142,46 +5146,50 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>emma.brown</t>
+          <t>grace.smith</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Emma Brown</t>
+          <t>Grace Smith</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>11.01.2026</t>
+          <t>20.01.2026</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>11.01.2026 12:48</t>
+          <t>30.01.2026 12:25</t>
         </is>
       </c>
       <c r="H13" s="9" t="n">
-        <v>1</v>
+        <v>240</v>
       </c>
       <c r="I13" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="J13" s="10" t="inlineStr">
-        <is>
-          <t>Compliant</t>
-        </is>
-      </c>
-      <c r="K13" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L13" s="9" t="n"/>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
+        </is>
+      </c>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>Terminated user retained access for 10 day(s) - SECURITY RISK</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -5196,46 +5204,50 @@
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>frank.garcia</t>
+          <t>henry.johnson</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Frank Garcia</t>
+          <t>Henry Johnson</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>15.12.2025</t>
+          <t>09.01.2026</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>15.12.2025 11:48</t>
+          <t>15.01.2026 12:25</t>
         </is>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="I14" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>Compliant</t>
-        </is>
-      </c>
-      <c r="K14" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="n"/>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
+        </is>
+      </c>
+      <c r="K14" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>Terminated user retained access for 6 day(s) - SECURITY RISK</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -5250,31 +5262,31 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>henry.williams</t>
+          <t>henry.jones</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Henry Williams</t>
+          <t>Henry Jones</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>23.01.2026</t>
+          <t>07.02.2026</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>23.01.2026 18:48</t>
+          <t>07.02.2026 23:25</t>
         </is>
       </c>
       <c r="H15" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I15" s="9" t="n">
         <v>24</v>
@@ -5304,12 +5316,12 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>frank.brown</t>
+          <t>alice.williams</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Frank Brown</t>
+          <t>Alice Williams</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -5319,16 +5331,16 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>17.01.2026</t>
+          <t>11.01.2026</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>17.01.2026 18:48</t>
+          <t>11.01.2026 23:25</t>
         </is>
       </c>
       <c r="H16" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I16" s="9" t="n">
         <v>24</v>
@@ -5358,46 +5370,50 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>bob.garcia</t>
+          <t>bob.williams</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Bob Garcia</t>
+          <t>Bob Williams</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>28.01.2026</t>
+          <t>14.01.2026</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>28.01.2026 15:48</t>
+          <t>21.01.2026 12:25</t>
         </is>
       </c>
       <c r="H17" s="9" t="n">
-        <v>4</v>
+        <v>168</v>
       </c>
       <c r="I17" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="J17" s="10" t="inlineStr">
-        <is>
-          <t>Compliant</t>
-        </is>
-      </c>
-      <c r="K17" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L17" s="9" t="n"/>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
+        </is>
+      </c>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>Terminated user retained access for 7 day(s) - SECURITY RISK</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
@@ -5412,31 +5428,31 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>emma.johnson</t>
+          <t>carol.brown</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Emma Johnson</t>
+          <t>Carol Brown</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>20.12.2025</t>
+          <t>23.01.2026</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>20.12.2025 19:48</t>
+          <t>23.01.2026 17:25</t>
         </is>
       </c>
       <c r="H18" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I18" s="9" t="n">
         <v>24</v>
@@ -5466,46 +5482,50 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>frank.johnson</t>
+          <t>bob.johnson</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Frank Johnson</t>
+          <t>Bob Johnson</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>10.01.2026</t>
+          <t>06.02.2026</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>10.01.2026 15:48</t>
+          <t>11.02.2026 12:25</t>
         </is>
       </c>
       <c r="H19" s="9" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="I19" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="J19" s="10" t="inlineStr">
-        <is>
-          <t>Compliant</t>
-        </is>
-      </c>
-      <c r="K19" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L19" s="9" t="n"/>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
+        </is>
+      </c>
+      <c r="K19" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>Terminated user retained access for 5 day(s) - SECURITY RISK</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -5520,31 +5540,31 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>bob.williams</t>
+          <t>alice.garcia</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Bob Williams</t>
+          <t>Alice Garcia</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>10.12.2025</t>
+          <t>25.01.2026</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>10.12.2025 21:48</t>
+          <t>25.01.2026 13:25</t>
         </is>
       </c>
       <c r="H20" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I20" s="9" t="n">
         <v>24</v>
@@ -5574,31 +5594,31 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>bob.johnson</t>
+          <t>carol.williams</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Bob Johnson</t>
+          <t>Carol Williams</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>06.01.2026</t>
+          <t>14.12.2025</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>06.01.2026 19:48</t>
+          <t>14.12.2025 19:25</t>
         </is>
       </c>
       <c r="H21" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I21" s="9" t="n">
         <v>24</v>
@@ -5628,31 +5648,31 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>frank.johnson</t>
+          <t>carol.brown</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Frank Johnson</t>
+          <t>Carol Brown</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>15.12.2025</t>
+          <t>04.01.2026</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>15.12.2025 17:48</t>
+          <t>04.01.2026 23:25</t>
         </is>
       </c>
       <c r="H22" s="9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>24</v>
@@ -5682,17 +5702,17 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>alice.brown</t>
+          <t>bob.smith</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Alice Brown</t>
+          <t>Bob Smith</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
@@ -5702,7 +5722,7 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>01.01.2026 16:48</t>
+          <t>01.01.2026 17:25</t>
         </is>
       </c>
       <c r="H23" s="9" t="n">
@@ -5736,31 +5756,31 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>emma.johnson</t>
+          <t>frank.garcia</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Emma Johnson</t>
+          <t>Frank Garcia</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>21.12.2025</t>
+          <t>04.01.2026</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>21.12.2025 22:48</t>
+          <t>04.01.2026 20:25</t>
         </is>
       </c>
       <c r="H24" s="9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>24</v>
@@ -5790,27 +5810,27 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>emma.garcia</t>
+          <t>alice.williams</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Emma Garcia</t>
+          <t>Alice Williams</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>15.01.2026</t>
+          <t>05.01.2026</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>15.01.2026 20:48</t>
+          <t>05.01.2026 21:25</t>
         </is>
       </c>
       <c r="H25" s="9" t="n">
@@ -5844,31 +5864,31 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>emma.garcia</t>
+          <t>carol.garcia</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Emma Garcia</t>
+          <t>Carol Garcia</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>26.12.2025</t>
+          <t>29.12.2025</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>26.12.2025 17:48</t>
+          <t>29.12.2025 20:25</t>
         </is>
       </c>
       <c r="H26" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I26" s="9" t="n">
         <v>24</v>
@@ -5898,12 +5918,12 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>henry.johnson</t>
+          <t>carol.brown</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Henry Johnson</t>
+          <t>Carol Brown</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -5913,12 +5933,12 @@
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>31.12.2025</t>
+          <t>29.01.2026</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>31.12.2025 12:48</t>
+          <t>29.01.2026 13:25</t>
         </is>
       </c>
       <c r="H27" s="9" t="n">
@@ -5952,31 +5972,31 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>emma.jones</t>
+          <t>grace.brown</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Emma Jones</t>
+          <t>Grace Brown</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>24.01.2026</t>
+          <t>25.12.2025</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>24.01.2026 22:48</t>
+          <t>25.12.2025 20:25</t>
         </is>
       </c>
       <c r="H28" s="9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I28" s="9" t="n">
         <v>24</v>
@@ -6006,46 +6026,50 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>alice.brown</t>
+          <t>frank.johnson</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Alice Brown</t>
+          <t>Frank Johnson</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>11.01.2026</t>
+          <t>20.12.2025</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>11.01.2026 22:48</t>
+          <t>29.12.2025 12:25</t>
         </is>
       </c>
       <c r="H29" s="9" t="n">
-        <v>11</v>
+        <v>216</v>
       </c>
       <c r="I29" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="J29" s="10" t="inlineStr">
-        <is>
-          <t>Compliant</t>
-        </is>
-      </c>
-      <c r="K29" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L29" s="9" t="n"/>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
+        </is>
+      </c>
+      <c r="K29" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>Terminated user retained access for 9 day(s) - SECURITY RISK</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
@@ -6060,31 +6084,31 @@
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>grace.smith</t>
+          <t>alice.jones</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Grace Smith</t>
+          <t>Alice Jones</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>05.01.2026</t>
+          <t>16.12.2025</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>05.01.2026 12:48</t>
+          <t>16.12.2025 21:25</t>
         </is>
       </c>
       <c r="H30" s="9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I30" s="9" t="n">
         <v>24</v>
@@ -6114,31 +6138,31 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>david.brown</t>
+          <t>bob.smith</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>David Brown</t>
+          <t>Bob Smith</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>14.12.2025</t>
+          <t>19.12.2025</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>14.12.2025 12:48</t>
+          <t>19.12.2025 20:25</t>
         </is>
       </c>
       <c r="H31" s="9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I31" s="9" t="n">
         <v>24</v>
@@ -6168,12 +6192,12 @@
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>carol.brown</t>
+          <t>henry.smith</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Carol Brown</t>
+          <t>Henry Smith</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -6183,12 +6207,12 @@
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>06.02.2026</t>
+          <t>18.01.2026</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>06.02.2026 15:48</t>
+          <t>18.01.2026 16:25</t>
         </is>
       </c>
       <c r="H32" s="9" t="n">
@@ -6222,50 +6246,46 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>henry.garcia</t>
+          <t>carol.brown</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Henry Garcia</t>
+          <t>Carol Brown</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>24.01.2026</t>
+          <t>18.01.2026</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>28.01.2026 11:48</t>
+          <t>18.01.2026 23:25</t>
         </is>
       </c>
       <c r="H33" s="9" t="n">
-        <v>96</v>
+        <v>11</v>
       </c>
       <c r="I33" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="J33" s="11" t="inlineStr">
-        <is>
-          <t>Non-Compliant</t>
-        </is>
-      </c>
-      <c r="K33" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="L33" s="9" t="inlineStr">
-        <is>
-          <t>Terminated user retained access for 4 day(s) - SECURITY RISK</t>
-        </is>
-      </c>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>Compliant</t>
+        </is>
+      </c>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
@@ -6280,31 +6300,31 @@
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>alice.williams</t>
+          <t>alice.johnson</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Alice Williams</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>24.01.2026</t>
+          <t>31.12.2025</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>24.01.2026 13:48</t>
+          <t>31.12.2025 17:25</t>
         </is>
       </c>
       <c r="H34" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I34" s="9" t="n">
         <v>24</v>
@@ -6334,31 +6354,31 @@
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>bob.smith</t>
+          <t>bob.jones</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Bob Smith</t>
+          <t>Bob Jones</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>30.12.2025</t>
+          <t>05.01.2026</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>30.12.2025 23:48</t>
+          <t>05.01.2026 21:25</t>
         </is>
       </c>
       <c r="H35" s="9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I35" s="9" t="n">
         <v>24</v>
@@ -6491,50 +6511,50 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>EXT-bob.williams</t>
+          <t>EXT-emma.williams</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Bob Williams</t>
+          <t>Emma Williams</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Marketing Manager</t>
+          <t>IT Manager</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>21.05.2025</t>
+          <t>24.05.2025</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>21.02.2026</t>
         </is>
       </c>
       <c r="H6" s="9" t="n">
-        <v>151</v>
+        <v>12</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Expiring Soon</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>Compliant</t>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>Warning</t>
         </is>
       </c>
     </row>
@@ -6546,36 +6566,36 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>EXT-henry.garcia</t>
+          <t>EXT-henry.jones</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Henry Garcia</t>
+          <t>Henry Jones</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>Operations Manager</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>24.08.2025</t>
+          <t>01.08.2025</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>21.06.2026</t>
+          <t>12.03.2026</t>
         </is>
       </c>
       <c r="H7" s="9" t="n">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
@@ -6601,40 +6621,40 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>EXT-emma.brown</t>
+          <t>EXT-grace.smith</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Emma Brown</t>
+          <t>Grace Smith</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>IT Manager</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>08.11.2025</t>
+          <t>09.02.2025</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>12.01.2026</t>
+          <t>20.04.2026</t>
         </is>
       </c>
       <c r="H8" s="9" t="n">
-        <v>-28</v>
+        <v>70</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>EXPIRED</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="J8" s="9" t="inlineStr">
@@ -6642,9 +6662,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>Non-Compliant</t>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>Compliant</t>
         </is>
       </c>
     </row>
@@ -6656,36 +6676,36 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>EXT-bob.williams</t>
+          <t>EXT-grace.williams</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Bob Williams</t>
+          <t>Grace Williams</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>Operations Manager</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>22.06.2025</t>
+          <t>20.09.2025</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>04.04.2026</t>
+          <t>21.05.2026</t>
         </is>
       </c>
       <c r="H9" s="9" t="n">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
@@ -6711,36 +6731,36 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>EXT-alice.johnson</t>
+          <t>EXT-emma.jones</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Alice Johnson</t>
+          <t>Emma Jones</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>12.07.2025</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>27.04.2026</t>
+          <t>25.05.2026</t>
         </is>
       </c>
       <c r="H10" s="9" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
@@ -6766,40 +6786,40 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>EXT-bob.brown</t>
+          <t>EXT-emma.jones</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Bob Brown</t>
+          <t>Emma Jones</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>30.05.2025</t>
+          <t>23.06.2025</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>29.01.2026</t>
         </is>
       </c>
       <c r="H11" s="9" t="n">
-        <v>145</v>
+        <v>-11</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>EXPIRED</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
@@ -6807,9 +6827,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr">
-        <is>
-          <t>Compliant</t>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
         </is>
       </c>
     </row>
@@ -6821,40 +6841,40 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>EXT-david.brown</t>
+          <t>EXT-david.garcia</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>David Brown</t>
+          <t>David Garcia</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Operations Manager</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>06.03.2025</t>
+          <t>10.04.2025</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>16.01.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="H12" s="9" t="n">
-        <v>-24</v>
+        <v>161</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>EXPIRED</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="J12" s="9" t="inlineStr">
@@ -6862,9 +6882,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>Non-Compliant</t>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>Compliant</t>
         </is>
       </c>
     </row>
@@ -6876,36 +6896,36 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>EXT-frank.brown</t>
+          <t>EXT-carol.garcia</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Frank Brown</t>
+          <t>Carol Garcia</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>IT Manager</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>19.04.2025</t>
+          <t>31.05.2025</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>09.06.2026</t>
         </is>
       </c>
       <c r="H13" s="9" t="n">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
@@ -6931,50 +6951,50 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>EXT-bob.williams</t>
+          <t>EXT-david.garcia</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Bob Williams</t>
+          <t>David Garcia</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>19.08.2025</t>
+          <t>08.04.2025</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>10.04.2026</t>
+          <t>11.03.2026</t>
         </is>
       </c>
       <c r="H14" s="9" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Expiring Soon</t>
         </is>
       </c>
       <c r="J14" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K14" s="10" t="inlineStr">
-        <is>
-          <t>Compliant</t>
+          <t>Not Requested</t>
+        </is>
+      </c>
+      <c r="K14" s="12" t="inlineStr">
+        <is>
+          <t>Warning</t>
         </is>
       </c>
     </row>
@@ -6986,36 +7006,36 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>EXT-frank.smith</t>
+          <t>EXT-emma.brown</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Frank Smith</t>
+          <t>Emma Brown</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>26.10.2025</t>
+          <t>09.02.2025</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>16.03.2026</t>
         </is>
       </c>
       <c r="H15" s="9" t="n">
-        <v>157</v>
+        <v>35</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
@@ -7041,36 +7061,36 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>EXT-frank.garcia</t>
+          <t>EXT-david.jones</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Frank Garcia</t>
+          <t>David Jones</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>IT Manager</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>12.06.2025</t>
+          <t>03.05.2025</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>11.07.2026</t>
+          <t>21.04.2026</t>
         </is>
       </c>
       <c r="H16" s="9" t="n">
-        <v>152</v>
+        <v>71</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
@@ -7096,36 +7116,36 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>EXT-grace.brown</t>
+          <t>EXT-grace.johnson</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Grace Brown</t>
+          <t>Grace Johnson</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Marketing Manager</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>08.08.2025</t>
+          <t>29.10.2025</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>11.04.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="H17" s="9" t="n">
-        <v>61</v>
+        <v>149</v>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
@@ -7151,50 +7171,50 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>EXT-grace.smith</t>
+          <t>EXT-carol.garcia</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Grace Smith</t>
+          <t>Carol Garcia</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Marketing Manager</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>14.02.2025</t>
+          <t>19.02.2025</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>25.02.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="H18" s="9" t="n">
-        <v>16</v>
+        <v>149</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>Expiring Soon</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="K18" s="12" t="inlineStr">
-        <is>
-          <t>Warning</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>Compliant</t>
         </is>
       </c>
     </row>
@@ -7206,36 +7226,36 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>EXT-david.johnson</t>
+          <t>EXT-grace.smith</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>David Johnson</t>
+          <t>Grace Smith</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>IT Manager</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>07.06.2025</t>
+          <t>25.04.2025</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>08.05.2026</t>
+          <t>22.03.2026</t>
         </is>
       </c>
       <c r="H19" s="9" t="n">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
@@ -7261,36 +7281,36 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>EXT-david.johnson</t>
+          <t>EXT-henry.garcia</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>David Johnson</t>
+          <t>Henry Garcia</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Marketing Manager</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>20.08.2025</t>
+          <t>21.08.2025</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>09.06.2026</t>
+          <t>25.06.2026</t>
         </is>
       </c>
       <c r="H20" s="9" t="n">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
@@ -7316,36 +7336,36 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>EXT-henry.johnson</t>
+          <t>EXT-bob.brown</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Henry Johnson</t>
+          <t>Bob Brown</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>Operations Manager</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>27.07.2025</t>
+          <t>09.08.2025</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>30.05.2026</t>
+          <t>18.04.2026</t>
         </is>
       </c>
       <c r="H21" s="9" t="n">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
@@ -7371,50 +7391,50 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>EXT-david.brown</t>
+          <t>EXT-david.garcia</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>David Brown</t>
+          <t>David Garcia</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>16.07.2025</t>
+          <t>24.04.2025</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>03.03.2026</t>
         </is>
       </c>
       <c r="H22" s="9" t="n">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Expiring Soon</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>Compliant</t>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>Warning</t>
         </is>
       </c>
     </row>
@@ -7426,50 +7446,50 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>EXT-grace.johnson</t>
+          <t>EXT-alice.johnson</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Grace Johnson</t>
+          <t>Alice Johnson</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>17.09.2025</t>
+          <t>03.06.2025</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>09.02.2026</t>
+          <t>23.01.2026</t>
         </is>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>Expiring Soon</t>
+          <t>EXPIRED</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="K23" s="12" t="inlineStr">
-        <is>
-          <t>Warning</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="11" t="inlineStr">
+        <is>
+          <t>Non-Compliant</t>
         </is>
       </c>
     </row>
@@ -7481,36 +7501,36 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>EXT-emma.johnson</t>
+          <t>EXT-henry.johnson</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Emma Johnson</t>
+          <t>Henry Johnson</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Operations Manager</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>11.05.2025</t>
+          <t>26.05.2025</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>30.06.2026</t>
+          <t>25.07.2026</t>
         </is>
       </c>
       <c r="H24" s="9" t="n">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
@@ -7536,36 +7556,36 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>EXT-grace.williams</t>
+          <t>EXT-emma.williams</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Grace Williams</t>
+          <t>Emma Williams</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>01.04.2025</t>
+          <t>11.05.2025</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>16.03.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="H25" s="9" t="n">
-        <v>35</v>
+        <v>161</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
@@ -7591,36 +7611,36 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>EXT-henry.williams</t>
+          <t>EXT-grace.jones</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Henry Williams</t>
+          <t>Grace Jones</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Sales Manager</t>
+          <t>Engineering Manager</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>13.07.2025</t>
+          <t>27.05.2025</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>29.05.2026</t>
+          <t>13.05.2026</t>
         </is>
       </c>
       <c r="H26" s="9" t="n">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
@@ -7646,36 +7666,36 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>EXT-grace.garcia</t>
+          <t>EXT-carol.williams</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Grace Garcia</t>
+          <t>Carol Williams</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>07.08.2025</t>
+          <t>19.03.2025</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>18.03.2026</t>
+          <t>11.06.2026</t>
         </is>
       </c>
       <c r="H27" s="9" t="n">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
@@ -7701,36 +7721,36 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>EXT-grace.jones</t>
+          <t>EXT-alice.smith</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Grace Jones</t>
+          <t>Alice Smith</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Operations Manager</t>
+          <t>Sales Manager</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>01.11.2025</t>
+          <t>01.03.2025</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>06.05.2026</t>
+          <t>13.06.2026</t>
         </is>
       </c>
       <c r="H28" s="9" t="n">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
@@ -7756,50 +7776,50 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>EXT-emma.garcia</t>
+          <t>EXT-henry.johnson</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Emma Garcia</t>
+          <t>Henry Johnson</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>IT Manager</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>22.04.2025</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>14.02.2026</t>
+          <t>06.04.2026</t>
         </is>
       </c>
       <c r="H29" s="9" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>Expiring Soon</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>Not Requested</t>
-        </is>
-      </c>
-      <c r="K29" s="12" t="inlineStr">
-        <is>
-          <t>Warning</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="inlineStr">
+        <is>
+          <t>Compliant</t>
         </is>
       </c>
     </row>
@@ -7811,36 +7831,36 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>EXT-david.brown</t>
+          <t>EXT-bob.johnson</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>David Brown</t>
+          <t>Bob Johnson</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>IT Manager</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>24.10.2025</t>
+          <t>10.06.2025</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>28.06.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="H30" s="9" t="n">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
@@ -7974,22 +7994,22 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>frank.williams</t>
+          <t>emma.brown</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>18.06.2025</t>
+          <t>09.08.2025</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>22.01.2026</t>
+          <t>10.01.2026</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -7999,7 +8019,7 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>IT Operations</t>
+          <t>Department Manager</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -8023,50 +8043,44 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>emma.smith</t>
+          <t>henry.jones</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>01.04.2025</t>
+          <t>25.09.2025</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>07.02.2026</t>
+          <t>10.01.2026</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>No login for 120+ days</t>
+          <t>Contractor contract ended, account still active</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>IT Operations</t>
+          <t>Security Team</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>Reassign owner</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>15.02.2026</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>Remediated</t>
+          <t>Document exception</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr"/>
+      <c r="J7" s="9" t="inlineStr"/>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -8078,27 +8092,27 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>david.smith</t>
+          <t>emma.garcia</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>31.03.2025</t>
+          <t>07.05.2025</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>18.01.2026</t>
+          <t>06.02.2026</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>User terminated but account not disabled</t>
+          <t>Contractor contract ended, account still active</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -8108,16 +8122,16 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>Delete account</t>
+          <t>Document exception</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>25.01.2026</t>
+          <t>14.02.2026</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K8" s="10" t="inlineStr">
         <is>
@@ -8133,32 +8147,32 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>bob.brown</t>
+          <t>david.johnson</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>24.03.2025</t>
+          <t>07.05.2025</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>17.01.2026</t>
+          <t>29.01.2026</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>User terminated but account not disabled</t>
+          <t>No login for 120+ days</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>Security Team</t>
+          <t>Department Manager</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
@@ -8166,11 +8180,17 @@
           <t>Disable account</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr"/>
-      <c r="J9" s="9" t="inlineStr"/>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>02.02.2026</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>Remediated</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8202,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>henry.smith</t>
+          <t>frank.garcia</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -8192,27 +8212,27 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>22.10.2025</t>
+          <t>03.07.2025</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>03.02.2026</t>
+          <t>12.01.2026</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>No login for 120+ days</t>
+          <t>No valid business owner</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>Department Manager</t>
+          <t>IT Operations</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>Document exception</t>
+          <t>Reassign owner</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr"/>
@@ -8231,7 +8251,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>bob.jones</t>
+          <t>grace.smith</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -8241,27 +8261,27 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>12.06.2025</t>
+          <t>08.10.2025</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>30.01.2026</t>
+          <t>17.01.2026</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Contractor contract ended, account still active</t>
+          <t>No valid business owner</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>IT Operations</t>
+          <t>Security Team</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>Document exception</t>
+          <t>Reassign owner</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr"/>
@@ -8280,27 +8300,27 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>alice.smith</t>
+          <t>frank.jones</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>07.11.2025</t>
+          <t>28.05.2025</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>12.01.2026</t>
+          <t>02.02.2026</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>No valid business owner</t>
+          <t>Contractor contract ended, account still active</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -8310,14 +8330,20 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>Delete account</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="inlineStr"/>
-      <c r="J12" s="9" t="inlineStr"/>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>Disable account</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>09.02.2026</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>Remediated</t>
         </is>
       </c>
     </row>
@@ -8329,7 +8355,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>carol.johnson</t>
+          <t>grace.smith</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -8339,7 +8365,7 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>23.10.2025</t>
+          <t>07.03.2025</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -8349,7 +8375,7 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>No login for 120+ days</t>
+          <t>No valid business owner</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -8359,14 +8385,20 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>Reassign owner</t>
-        </is>
-      </c>
-      <c r="I13" s="9" t="inlineStr"/>
-      <c r="J13" s="9" t="inlineStr"/>
-      <c r="K13" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>Delete account</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>24.01.2026</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>Remediated</t>
         </is>
       </c>
     </row>
@@ -8378,22 +8410,22 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>alice.garcia</t>
+          <t>emma.brown</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Contractor</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>27.05.2025</t>
+          <t>05.10.2025</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>21.01.2026</t>
+          <t>14.01.2026</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
@@ -8408,20 +8440,14 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>Reassign owner</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>29.01.2026</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="K14" s="10" t="inlineStr">
-        <is>
-          <t>Remediated</t>
+          <t>Delete account</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr"/>
+      <c r="J14" s="9" t="inlineStr"/>
+      <c r="K14" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -8433,22 +8459,22 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>carol.jones</t>
+          <t>bob.jones</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Contractor</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>14.07.2025</t>
+          <t>01.08.2025</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>02.02.2026</t>
+          <t>28.01.2026</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
@@ -8458,12 +8484,12 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>IT Operations</t>
+          <t>Security Team</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>Reassign owner</t>
+          <t>Delete account</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
@@ -8472,7 +8498,7 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K15" s="10" t="inlineStr">
         <is>
@@ -8488,7 +8514,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>grace.garcia</t>
+          <t>henry.williams</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -8498,12 +8524,12 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>07.07.2025</t>
+          <t>08.05.2025</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>16.01.2026</t>
+          <t>13.01.2026</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
@@ -8513,25 +8539,19 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>Department Manager</t>
+          <t>Security Team</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>Reassign owner</t>
-        </is>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>23.01.2026</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="K16" s="10" t="inlineStr">
-        <is>
-          <t>Remediated</t>
+          <t>Disable account</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr"/>
+      <c r="J16" s="9" t="inlineStr"/>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -8543,50 +8563,44 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>bob.smith</t>
+          <t>bob.johnson</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>07.09.2025</t>
+          <t>07.11.2025</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>24.01.2026</t>
+          <t>13.01.2026</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>User terminated but account not disabled</t>
+          <t>No login for 120+ days</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>Department Manager</t>
+          <t>IT Operations</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>Document exception</t>
-        </is>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>26.01.2026</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" s="10" t="inlineStr">
-        <is>
-          <t>Remediated</t>
+          <t>Reassign owner</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr"/>
+      <c r="J17" s="9" t="inlineStr"/>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8612,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>grace.smith</t>
+          <t>david.garcia</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -8608,40 +8622,34 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>08.08.2025</t>
+          <t>15.09.2025</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>17.01.2026</t>
+          <t>13.01.2026</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>No login for 120+ days</t>
+          <t>Contractor contract ended, account still active</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>Security Team</t>
+          <t>Department Manager</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>Reassign owner</t>
-        </is>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>27.01.2026</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="K18" s="10" t="inlineStr">
-        <is>
-          <t>Remediated</t>
+          <t>Delete account</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr"/>
+      <c r="J18" s="9" t="inlineStr"/>
+      <c r="K18" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -8653,22 +8661,22 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>emma.johnson</t>
+          <t>grace.garcia</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Service Account</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>28.05.2025</t>
+          <t>10.07.2025</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>18.01.2026</t>
+          <t>10.01.2026</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
@@ -8678,7 +8686,7 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>Security Team</t>
+          <t>Department Manager</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
@@ -8702,22 +8710,22 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>bob.garcia</t>
+          <t>david.brown</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Contractor</t>
+          <t>Service Account</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>14.09.2025</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>03.02.2026</t>
+          <t>07.02.2026</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
@@ -8727,25 +8735,19 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>IT Operations</t>
+          <t>Department Manager</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>Disable account</t>
-        </is>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>11.02.2026</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="K20" s="10" t="inlineStr">
-        <is>
-          <t>Remediated</t>
+          <t>Reassign owner</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr"/>
+      <c r="J20" s="9" t="inlineStr"/>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9097,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>08.02.2026 10:48</t>
+          <t>08.02.2026 11:25</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -9132,7 +9134,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>07.02.2026 11:48</t>
+          <t>07.02.2026 12:25</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -9206,7 +9208,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>05.02.2026 11:48</t>
+          <t>05.02.2026 12:25</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -9243,7 +9245,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>08.02.2026 11:18</t>
+          <t>08.02.2026 11:55</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
